--- a/02_Scraping_longchau_playwright/products.xlsx
+++ b/02_Scraping_longchau_playwright/products.xlsx
@@ -413,169 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-ho-tro-cai-thien-suc-de-khang-cho-co-the-zincelite-vitamins-for-life-30-v.html</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Locator.wait_for: Target page, context or browser has been closed
-Call log:
-  - waiting for locator("[data-test=\"product_name\"]").first to be visible
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/siro-ho-tro-hap-thu-canxi-giup-xuong-rang-chac-khoe-nature-s-way-kids-smart-drops-vitamin-d3-k2-11-ml.html</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-ho-tro-giam-met-moi-active-nerves-new-nordic-30-v.html</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/nature-s-way-kids-smart-liquid-zinc-100-ml.html</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/bo-sung-vitamin-d3-ho-tro-xuong-rang-d3-drops-dao-nordic-health-10-ml.html</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-bo-sung-vitamin-va-khoang-chat-easylife-immuvita-100-v.html</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/siro-bo-sung-canxi-d3-k2-kingphar-6-x5-ong.html</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/siro-brauer-baby-kids-d3-k2-high-potency-mk-7-drops-10-ml.html</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-ho-tro-nao-bo-thi-luc-va-suc-khoe-tim-mach-omega-3-plus-kenko-120-v.html</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-bo-sung-omega-3-6-9-premium-omexxel-100-v.html</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-nhai-ho-tro-su-phat-trien-xuong-cho-tre-em-borne-mineral-new-nordic-120-v.html</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-bo-sung-canxi-giam-nguy-co-loang-xuong-calcium-premium-jpanwell-120-v.html</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Page.goto: Target page, context or browser has been closed</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>